--- a/pregenereated_results/s2/att_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/pregenereated_results/s2/att_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covariate_Balance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weight_Diagnostics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATT_MSM" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Propensity_Model" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Covariate_Balance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weight_Diagnostics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ATT_MSM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Propensity_Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,13 +480,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.011</v>
+        <v>-0.019</v>
       </c>
       <c r="D2" t="n">
         <v>-0.002</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.043</v>
+        <v>-0.037</v>
       </c>
       <c r="D3" t="n">
         <v>0.003</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03999999999999999</v>
+        <v>0.034</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.044</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E4" t="n">
-        <v>0.042</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -552,22 +552,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.097</v>
+        <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.003</v>
+        <v>0.001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.094</v>
+        <v>0.045</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -579,22 +579,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.027</v>
+        <v>0.097</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="E6" t="n">
-        <v>0.025</v>
+        <v>0.094</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.043</v>
+        <v>-0.024</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E7" t="n">
-        <v>0.042</v>
+        <v>0.022</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.02</v>
+        <v>0.046</v>
       </c>
       <c r="D8" t="n">
-        <v>-0</v>
+        <v>-0.001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02</v>
+        <v>0.045</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.081</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.078</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.038</v>
+        <v>-0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="E10" t="n">
-        <v>0.037</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.028</v>
+        <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.008</v>
+        <v>0.023</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="E12" t="n">
-        <v>0.007</v>
+        <v>0.019</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.045</v>
+        <v>0.007</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.008</v>
+        <v>0.001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.037</v>
+        <v>0.006</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.007</v>
+        <v>0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>0.007</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.029</v>
+        <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.005</v>
+        <v>0.007</v>
       </c>
       <c r="E15" t="n">
-        <v>0.024</v>
+        <v>-0.002</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.01</v>
+        <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="E16" t="n">
-        <v>0.008</v>
+        <v>0.028</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0</v>
+        <v>-0.014</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.004</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.075</v>
+        <v>-0.008</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E19" t="n">
-        <v>0.074</v>
+        <v>0.006</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.019</v>
+        <v>0.077</v>
       </c>
       <c r="D20" t="n">
         <v>-0.001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.018</v>
+        <v>0.076</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.109</v>
+        <v>-0.019</v>
       </c>
       <c r="D21" t="n">
-        <v>0.003</v>
+        <v>-0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.106</v>
+        <v>0.019</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.19</v>
+        <v>-0.113</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="E22" t="n">
-        <v>0.184</v>
+        <v>0.11</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.146</v>
+        <v>0.197</v>
       </c>
       <c r="D23" t="n">
-        <v>0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="E23" t="n">
-        <v>0.143</v>
+        <v>0.191</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.051</v>
+        <v>-0.143</v>
       </c>
       <c r="D24" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="E24" t="n">
-        <v>0.045</v>
+        <v>0.14</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.118</v>
+        <v>-0.054</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.003</v>
+        <v>0.006</v>
       </c>
       <c r="E25" t="n">
-        <v>0.115</v>
+        <v>0.048</v>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.218</v>
+        <v>-0.128</v>
       </c>
       <c r="D26" t="n">
         <v>-0.002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.216</v>
+        <v>0.126</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Exceeds</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.254</v>
+        <v>0.227</v>
       </c>
       <c r="D27" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="E27" t="n">
-        <v>0.252</v>
+        <v>0.225</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Below</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.328</v>
+        <v>0.392</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.001</v>
+        <v>-0.008</v>
       </c>
       <c r="E28" t="n">
-        <v>0.327</v>
+        <v>0.384</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.436</v>
+        <v>-0.401</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.008</v>
+        <v>0.005</v>
       </c>
       <c r="E29" t="n">
-        <v>0.428</v>
+        <v>0.396</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.06</v>
+        <v>0.107</v>
       </c>
       <c r="D30" t="n">
-        <v>0.005</v>
+        <v>-0.003</v>
       </c>
       <c r="E30" t="n">
-        <v>0.055</v>
+        <v>0.104</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.108</v>
+        <v>-0.041</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.003</v>
+        <v>-0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.105</v>
+        <v>0.041</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.046</v>
+        <v>-0.066</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="E32" t="n">
-        <v>0.045</v>
+        <v>0.059</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,45 +1317,18 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.068</v>
+        <v>0.022</v>
       </c>
       <c r="D33" t="n">
-        <v>0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="E33" t="n">
-        <v>0.06200000000000001</v>
+        <v>0.018</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
       </c>
       <c r="G33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>region_North_America</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="F34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1412,16 +1385,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9000</v>
+        <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>541.114156846371</v>
+        <v>554.8319074166568</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0570484345693796</v>
+        <v>0.07201588164977409</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2255693013305237</v>
+        <v>0.2496221955703657</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -1444,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1491,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.240049365256666</v>
+        <v>2.236944464107626</v>
       </c>
       <c r="C2" t="n">
-        <v>0.344325386652665</v>
+        <v>0.3384250196146384</v>
       </c>
       <c r="D2" t="n">
-        <v>1.565184008454614</v>
+        <v>1.573643614195673</v>
       </c>
       <c r="E2" t="n">
-        <v>2.914914722058718</v>
+        <v>2.900245314019579</v>
       </c>
       <c r="F2" t="n">
-        <v>7.737472091452898e-11</v>
+        <v>3.846647276144932e-11</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1516,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1857511290617479</v>
+        <v>0.181150802664234</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06786141777990333</v>
+        <v>0.06590363351848991</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05274519427331131</v>
+        <v>0.05198205451766702</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3187570638501845</v>
+        <v>0.3103195508108009</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006196223144383357</v>
+        <v>0.005982800716697901</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1541,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2958593429467762</v>
+        <v>0.2889210511748292</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1516902558173703</v>
+        <v>0.152598570159998</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.001448095260936921</v>
+        <v>-0.01016665043107551</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5931667811544893</v>
+        <v>0.5880087527807341</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05112636717879238</v>
+        <v>0.05831260422500208</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1566,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.009044822957615242</v>
+        <v>-0.005957694933862404</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1176397630893518</v>
+        <v>0.1146433802895678</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2396145217625691</v>
+        <v>-0.2306545913673444</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2215248758473386</v>
+        <v>0.2187392014996196</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9387144234089405</v>
+        <v>0.9585548324340618</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1591,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2580187869264272</v>
+        <v>0.2614273190347506</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1399285404189768</v>
+        <v>0.1392840286028359</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0162361127040247</v>
+        <v>-0.01156436064845456</v>
       </c>
       <c r="E6" t="n">
-        <v>0.532273686556879</v>
+        <v>0.5344189987179557</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06519297424450356</v>
+        <v>0.06052675630473976</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1616,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.02160621808681999</v>
+        <v>-0.01841397076183374</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1244272034788676</v>
+        <v>0.122319336758662</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2654790556024374</v>
+        <v>-0.2581554654216376</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2222666194287974</v>
+        <v>0.2213275238979701</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8621441084643017</v>
+        <v>0.8803384800164817</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1641,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2125370181084633</v>
+        <v>0.1905247839024714</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1313200253910848</v>
+        <v>0.1312065100950983</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.04484550210694824</v>
+        <v>-0.06663525042111218</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4699195383238749</v>
+        <v>0.447684818226055</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1055621724980763</v>
+        <v>0.146474203287111</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1666,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1571928978068181</v>
+        <v>0.1647719700746341</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1147635469225392</v>
+        <v>0.1133318732696419</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.06773952089943122</v>
+        <v>-0.05735441983432171</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3821253165130675</v>
+        <v>0.3868983599835899</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1707771194512337</v>
+        <v>0.145977067888413</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1691,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1911563125249384</v>
+        <v>-0.2220479403681949</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1818983361688493</v>
+        <v>0.1738904480020734</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5476705002636425</v>
+        <v>-0.5628669557077937</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1653578752137657</v>
+        <v>0.118771074971404</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2933061591520859</v>
+        <v>0.2016228791937926</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1716,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02965315615332592</v>
+        <v>0.03288756718509728</v>
       </c>
       <c r="C11" t="n">
-        <v>0.178419770103641</v>
+        <v>0.1776097727247108</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3200431673797267</v>
+        <v>-0.3152211906576804</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3793494796863785</v>
+        <v>0.3809963250278749</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8680004840790592</v>
+        <v>0.8530976171323723</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1741,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.02825157817888525</v>
+        <v>-0.01926300923725715</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1877170939834104</v>
+        <v>0.185793753035985</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3961703216688902</v>
+        <v>-0.3834120737403171</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3396671653111197</v>
+        <v>0.3448860552658028</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8803694970892808</v>
+        <v>0.917423670738676</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1766,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01931853626025872</v>
+        <v>0.02751012339829574</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1636070204289303</v>
+        <v>0.1635058900678629</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3013453313983536</v>
+        <v>-0.2929555323948809</v>
       </c>
       <c r="E13" t="n">
-        <v>0.339982403918871</v>
+        <v>0.3479757791914724</v>
       </c>
       <c r="F13" t="n">
-        <v>0.906005145444313</v>
+        <v>0.8663853688450225</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1791,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2267586099298788</v>
+        <v>-0.2140509916498261</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1996903763893022</v>
+        <v>0.1996415110470127</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6181445557121586</v>
+        <v>-0.6053411631211263</v>
       </c>
       <c r="E14" t="n">
-        <v>0.164627335852401</v>
+        <v>0.1772391798214742</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2561445190800596</v>
+        <v>0.2836406395758082</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1816,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1064679161252029</v>
+        <v>0.1171045186779468</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1682200947144058</v>
+        <v>0.1619967599285946</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2232374109909492</v>
+        <v>-0.2004032963942799</v>
       </c>
       <c r="E15" t="n">
-        <v>0.436173243241355</v>
+        <v>0.4346123337501736</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5267934421272666</v>
+        <v>0.4697524708434638</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1841,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.01207466849072311</v>
+        <v>-0.01272868241196943</v>
       </c>
       <c r="C16" t="n">
-        <v>0.168783776517552</v>
+        <v>0.1645558921490829</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3428847916397824</v>
+        <v>-0.3352523044680294</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3187354546583361</v>
+        <v>0.3097949396440905</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9429685701055445</v>
+        <v>0.9383437421023137</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1866,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.03252953174811903</v>
+        <v>-0.04675708148500214</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1751028005614567</v>
+        <v>0.1760312745689469</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3757247144406741</v>
+        <v>-0.3917720397928196</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3106656509444361</v>
+        <v>0.2982578768228153</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8526220658937762</v>
+        <v>0.7905333934586961</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1891,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.03731818459860319</v>
+        <v>-0.0230194693438065</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1722486534581974</v>
+        <v>0.1644652153812265</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3749193417621907</v>
+        <v>-0.3453653682006333</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3002829725649843</v>
+        <v>0.2993264295130204</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8284787917365297</v>
+        <v>0.8886871854160932</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1916,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.2225424893624058</v>
+        <v>-0.2146921070890922</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1684576646932614</v>
+        <v>0.1515530665957196</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5527134450809228</v>
+        <v>-0.511730659363303</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1076284663561112</v>
+        <v>0.08234644518511855</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1864817412944128</v>
+        <v>0.1565959844710106</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1941,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.005384634480381373</v>
+        <v>-0.005402522655627922</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1713798180465601</v>
+        <v>0.1655922621823108</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.330513636567904</v>
+        <v>-0.329957392651471</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3412829055286668</v>
+        <v>0.3191523473402152</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9749351469538294</v>
+        <v>0.9739732716462245</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1966,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2638160265751596</v>
+        <v>-0.2427296873564389</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1696051255710189</v>
+        <v>0.1660896874446663</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5962359642877501</v>
+        <v>-0.5682594929514991</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06860391113743092</v>
+        <v>0.08280011823862143</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1198336942965845</v>
+        <v>0.1438954327129224</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1991,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.03365759344275049</v>
+        <v>-0.03768411407691187</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1812041225956656</v>
+        <v>0.1797730666913064</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3888111475804357</v>
+        <v>-0.3900328501821896</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3214959606949347</v>
+        <v>0.3146646220283659</v>
       </c>
       <c r="F22" t="n">
-        <v>0.852645457208707</v>
+        <v>0.8339639046817264</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -2016,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.05564134963204054</v>
+        <v>-0.02464806102588238</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1969943584205157</v>
+        <v>0.1900831223009973</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4417431972938259</v>
+        <v>-0.3972041348047595</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3304604980297449</v>
+        <v>0.3479080127529947</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7775973398126066</v>
+        <v>0.8968275912688044</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2037,23 +2010,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>performance_rating_Exceeds[T.True]</t>
+          <t>performance_rating_Far_Exceeds[T.True]</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0108332621591128</v>
+        <v>0.205941611377199</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05968151934673272</v>
+        <v>0.0952473837479588</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1278068906213394</v>
+        <v>0.01926016960953411</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1061403663031138</v>
+        <v>0.3926230531448639</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8559611093625814</v>
+        <v>0.03060460934207474</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2062,23 +2035,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Below[T.True]</t>
+          <t>performance_rating_Meets[T.True]</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0211731125484398</v>
+        <v>0.04452008568402004</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03934642864885833</v>
+        <v>0.07833813972634329</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.05594447052359751</v>
+        <v>-0.1090198467954792</v>
       </c>
       <c r="E25" t="n">
-        <v>0.09829069562047711</v>
+        <v>0.1980600181635193</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5904939887610445</v>
+        <v>0.5698267649268587</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2087,23 +2060,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds[T.True]</t>
+          <t>region_Europe[T.True]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1884735792582888</v>
+        <v>0.04831767222516972</v>
       </c>
       <c r="C26" t="n">
-        <v>0.06577189980788596</v>
+        <v>0.1075095082429103</v>
       </c>
       <c r="D26" t="n">
-        <v>0.05956302444005546</v>
+        <v>-0.1623970919265466</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3173841340765222</v>
+        <v>0.2590324363768861</v>
       </c>
       <c r="F26" t="n">
-        <v>0.004162673016683738</v>
+        <v>0.6531236814450416</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2112,23 +2085,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Meets[T.True]</t>
+          <t>region_Latin_America[T.True]</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.02278973461402843</v>
+        <v>0.01812015855057374</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03094114169455125</v>
+        <v>0.1120508625951185</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.03785378874784264</v>
+        <v>-0.2014954965725048</v>
       </c>
       <c r="E27" t="n">
-        <v>0.08343325797589951</v>
+        <v>0.2377358136736523</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4613953291819046</v>
+        <v>0.8715313227345118</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2137,23 +2110,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>region_Europe[T.True]</t>
+          <t>region_Middle_East_and_Africa[T.True]</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.05597085354441947</v>
+        <v>-0.04940558150093542</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1071641602497907</v>
+        <v>0.1079780618094178</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1540670409786491</v>
+        <v>-0.2610386937678341</v>
       </c>
       <c r="E28" t="n">
-        <v>0.266008748067488</v>
+        <v>0.1622275307659633</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6014678831736312</v>
+        <v>0.6472743129266689</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2162,23 +2135,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Latin_America[T.True]</t>
+          <t>region_North_America[T.True]</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.02411826297637243</v>
+        <v>0.04280137104231091</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1141604113037756</v>
+        <v>0.1082244098992596</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1996320316393071</v>
+        <v>-0.169314574608338</v>
       </c>
       <c r="E29" t="n">
-        <v>0.247868557592052</v>
+        <v>0.2549173166929598</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8326793737231943</v>
+        <v>0.6924833512519115</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2187,23 +2160,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa[T.True]</t>
+          <t>treatment</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.03917721632574485</v>
+        <v>0.4119231277135923</v>
       </c>
       <c r="C30" t="n">
-        <v>0.108108256570926</v>
+        <v>0.0355166202146675</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2510655056361754</v>
+        <v>0.3423118312402568</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1727110729846857</v>
+        <v>0.4815344241869278</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7170615427095536</v>
+        <v>4.216315028048566e-31</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2212,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_North_America[T.True]</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.05124452339044745</v>
+        <v>-0.005696864427362682</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1061310782053327</v>
+        <v>0.005018673731113935</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1567685675324085</v>
+        <v>-0.01553328419050325</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2592576143133034</v>
+        <v>0.004139555335777885</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6292080515422336</v>
+        <v>0.2563194081069056</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2237,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4117363946512974</v>
+        <v>-0.01025948591986663</v>
       </c>
       <c r="C32" t="n">
-        <v>0.03602010670634243</v>
+        <v>0.005466797757691124</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3411382827875765</v>
+        <v>-0.02097421263570556</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4823345065150182</v>
+        <v>0.0004552407959723011</v>
       </c>
       <c r="F32" t="n">
-        <v>2.936035288108103e-30</v>
+        <v>0.06056056299802003</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2262,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.01128559626780638</v>
+        <v>0.4575134647665858</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01401433545150976</v>
+        <v>0.04666760652833874</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.03875318902002838</v>
+        <v>0.3660466367263556</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01618199648441562</v>
+        <v>0.548980292806816</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4206526774246108</v>
+        <v>1.085758088206498e-22</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2287,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4637283169865087</v>
+        <v>-0.02794494020865268</v>
       </c>
       <c r="C34" t="n">
-        <v>0.04750875400491485</v>
+        <v>0.01461262990600847</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3706128701865025</v>
+        <v>-0.05658516854384221</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5568437637865149</v>
+        <v>0.0006952881265368388</v>
       </c>
       <c r="F34" t="n">
-        <v>1.656741928492521e-22</v>
+        <v>0.05582712904150877</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2312,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.01032062050632575</v>
+        <v>1.440174177203154</v>
       </c>
       <c r="C35" t="n">
-        <v>0.005504915105007049</v>
+        <v>0.1799506899318458</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0211100558500901</v>
+        <v>1.087477305943602</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0004688148374385904</v>
+        <v>1.792871048462706</v>
       </c>
       <c r="F35" t="n">
-        <v>0.06082010151265062</v>
+        <v>1.212661290945603e-15</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2337,50 +2310,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.00575757875347096</v>
+        <v>0.007976972803062383</v>
       </c>
       <c r="C36" t="n">
-        <v>0.004881000896562427</v>
+        <v>0.004378059075285193</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.01532416471924103</v>
+        <v>-0.0006038653066853285</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00380900721229911</v>
+        <v>0.01655781091281009</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2381634113120084</v>
+        <v>0.06844981601298357</v>
       </c>
       <c r="G36" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>is_new_manager</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1.459376417687799</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.1805877367954613</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1.105430957519096</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.813321877856501</v>
-      </c>
-      <c r="F37" t="n">
-        <v>6.410108433432522e-16</v>
-      </c>
-      <c r="G37" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2395,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2427,10 +2375,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-28.63902089506874</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+        <v>-2.680600179802938</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.4771933030981325</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.938181768271168e-08</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2439,13 +2391,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02313926327038869</v>
+        <v>-0.02542074333516161</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09767080877239748</v>
+        <v>0.1002143663033997</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8127260403169279</v>
+        <v>0.79975540801217</v>
       </c>
     </row>
     <row r="4">
@@ -2455,13 +2407,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2234052412627341</v>
+        <v>0.2244463748843409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2328794784675677</v>
+        <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3373990767846601</v>
+        <v>0.3364439424069159</v>
       </c>
     </row>
     <row r="5">
@@ -2471,13 +2423,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8180627404127788</v>
+        <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.168995369134968</v>
+        <v>0.1734026513921177</v>
       </c>
       <c r="D5" t="n">
-        <v>1.293561512468184e-06</v>
+        <v>2.563995828054277e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2487,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03544498749501269</v>
+        <v>0.03527526670387295</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1931765748363377</v>
+        <v>0.191688294691954</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8544175536043231</v>
+        <v>0.853994545471355</v>
       </c>
     </row>
     <row r="7">
@@ -2503,13 +2455,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2759060224168001</v>
+        <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1812662636985352</v>
+        <v>0.1901447102133382</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1279831380955545</v>
+        <v>0.1446466431125516</v>
       </c>
     </row>
     <row r="8">
@@ -2519,13 +2471,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1078851505725079</v>
+        <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1932040224873154</v>
+        <v>0.1952515666982443</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5765711865505436</v>
+        <v>0.5954095400432464</v>
       </c>
     </row>
     <row r="9">
@@ -2535,13 +2487,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8717785708706234</v>
+        <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1678649184861324</v>
+        <v>0.1695280942409136</v>
       </c>
       <c r="D9" t="n">
-        <v>2.065612399360983e-07</v>
+        <v>2.539495077342701e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2551,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.03735224036769266</v>
+        <v>-0.04456520772617086</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2698916793365708</v>
+        <v>0.2604021031716313</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8899265459788944</v>
+        <v>0.8641137091517834</v>
       </c>
     </row>
     <row r="11">
@@ -2567,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.27139852374157</v>
+        <v>-0.2737623724798149</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2816070636601529</v>
+        <v>0.2787881385465057</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3351717854029546</v>
+        <v>0.3261132423877617</v>
       </c>
     </row>
     <row r="12">
@@ -2583,13 +2535,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08472740319915269</v>
+        <v>0.08100487957118127</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2580923618181321</v>
+        <v>0.2596429772097166</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7426974963062474</v>
+        <v>0.7550514391424692</v>
       </c>
     </row>
     <row r="13">
@@ -2599,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0406830151843166</v>
+        <v>0.03917827337461736</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2611004769215555</v>
+        <v>0.2572958805743769</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8761799203818157</v>
+        <v>0.8789745077123745</v>
       </c>
     </row>
     <row r="14">
@@ -2615,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.0534569388448658</v>
+        <v>-0.05296103812307947</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2638638595233255</v>
+        <v>0.2610089865588713</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8394532566768507</v>
+        <v>0.8392062624375523</v>
       </c>
     </row>
     <row r="15">
@@ -2631,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1239335042278707</v>
+        <v>0.1181322726534159</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2599280592390572</v>
+        <v>0.2572294350577177</v>
       </c>
       <c r="D15" t="n">
-        <v>0.633505078402905</v>
+        <v>0.646055612898408</v>
       </c>
     </row>
     <row r="16">
@@ -2647,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.001862882312047092</v>
+        <v>-0.004000986240379581</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2575901874165238</v>
+        <v>0.2383903410311186</v>
       </c>
       <c r="D16" t="n">
-        <v>0.994229779892155</v>
+        <v>0.9866094604655129</v>
       </c>
     </row>
     <row r="17">
@@ -2663,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1116424378427602</v>
+        <v>0.1057185310395304</v>
       </c>
       <c r="C17" t="n">
-        <v>0.258655496780073</v>
+        <v>0.2543340222421748</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6660132573861222</v>
+        <v>0.6776529122567303</v>
       </c>
     </row>
     <row r="18">
@@ -2679,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1317171712347951</v>
+        <v>-0.1377694895733256</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2668604742478565</v>
+        <v>0.2636874203313626</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6216023562146854</v>
+        <v>0.6013412201546261</v>
       </c>
     </row>
     <row r="19">
@@ -2695,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02274331928771129</v>
+        <v>-0.02557154094223238</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2635260646471042</v>
+        <v>0.252759790153811</v>
       </c>
       <c r="D19" t="n">
-        <v>0.931224861952453</v>
+        <v>0.9194160355966675</v>
       </c>
     </row>
     <row r="20">
@@ -2711,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06665392434454051</v>
+        <v>-0.07344622569376427</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2656595207910754</v>
+        <v>0.267457860954101</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8018915682473747</v>
+        <v>0.7836169672222772</v>
       </c>
     </row>
     <row r="21">
@@ -2727,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.209601896539733</v>
+        <v>0.2063167170305059</v>
       </c>
       <c r="C21" t="n">
-        <v>0.248589943238082</v>
+        <v>0.244289653245072</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3991371664160996</v>
+        <v>0.3983578134719846</v>
       </c>
     </row>
     <row r="22">
@@ -2743,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1668969509213569</v>
+        <v>-0.1704634573362026</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2747515022959944</v>
+        <v>0.2696748454965904</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5435543655447144</v>
+        <v>0.5273167196806361</v>
       </c>
     </row>
     <row r="23">
@@ -2759,189 +2711,189 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4971940641809904</v>
+        <v>-0.5008110927334757</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2924423487833311</v>
+        <v>0.287067218044571</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0891038687082271</v>
+        <v>0.08105838975171785</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>performance_rating_Exceeds[T.True]</t>
+          <t>performance_rating_Far_Exceeds[T.True]</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26.21442552889307</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+        <v>0.9366864721074267</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1483430409733375</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.713396260923891e-10</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Below[T.True]</t>
+          <t>performance_rating_Meets[T.True]</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.05451611819325158</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+        <v>-0.5776106069409677</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1143619392421807</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.401383208103943e-07</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds[T.True]</t>
+          <t>region_Europe[T.True]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27.15437389964459</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+        <v>0.237316144844174</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1503781926377478</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1145360411757813</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Meets[T.True]</t>
+          <t>region_Latin_America[T.True]</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25.63696707854778</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+        <v>-0.04350476117998651</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1611879340386412</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.7872365295400213</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>region_Europe[T.True]</t>
+          <t>region_Middle_East_and_Africa[T.True]</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2375989005820465</v>
+        <v>-0.07514354096975732</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1483942012831661</v>
+        <v>0.1613683918223567</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1093473930477332</v>
+        <v>0.6414556246120151</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Latin_America[T.True]</t>
+          <t>region_North_America[T.True]</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.04390400011936763</v>
+        <v>0.09749293462742097</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1581709974633308</v>
+        <v>0.1543265796290165</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7813401518904401</v>
+        <v>0.5275624553510008</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa[T.True]</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.07706864556783545</v>
+        <v>-0.002418133412192873</v>
       </c>
       <c r="C30" t="n">
-        <v>0.157805034131052</v>
+        <v>0.007135781003458546</v>
       </c>
       <c r="D30" t="n">
-        <v>0.625281499853628</v>
+        <v>0.7347043603418277</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_North_America[T.True]</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.09735884295380272</v>
+        <v>-0.005012017390962195</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1528329758431298</v>
+        <v>0.008304876992455039</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5241067842931748</v>
+        <v>0.5461741835341576</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.02140998846971486</v>
+        <v>-0.004129656026475419</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02125751820943617</v>
+        <v>0.02222260881033174</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3138518697695356</v>
+        <v>0.8525770672961279</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.004963851467076696</v>
+        <v>0.2280638724458785</v>
       </c>
       <c r="C33" t="n">
-        <v>0.008295015527601023</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5495638837808257</v>
+        <v>0.04668969945129923</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.002369150025833512</v>
+        <v>0.006335499136474495</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007250684388762908</v>
+        <v>0.006871422968197181</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7438581373216515</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>is_new_manager</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0.2289921174550882</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.1106079911199388</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.03842392670154298</v>
+        <v>0.3565249957666435</v>
       </c>
     </row>
   </sheetData>
